--- a/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008414815340366153</v>
       </c>
       <c r="C2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>23402514</v>
+        <v>4371144</v>
       </c>
       <c r="L2" t="n">
-        <v>13821964</v>
+        <v>2348204</v>
       </c>
       <c r="M2" t="n">
-        <v>3564348</v>
+        <v>550190</v>
       </c>
       <c r="N2" t="n">
-        <v>214936</v>
+        <v>23704</v>
       </c>
       <c r="O2" t="n">
-        <v>2109025</v>
+        <v>343540</v>
       </c>
       <c r="P2" t="n">
-        <v>828518</v>
+        <v>136795</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999769926071167</v>
+        <v>0.9999730587005615</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9183107018470764</v>
+        <v>0.8509180545806885</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8356481790542603</v>
+        <v>0.708907425403595</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7946805357933044</v>
+        <v>0.6355875134468079</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5909819602966309</v>
+        <v>0.2858176529407501</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8310619592666626</v>
+        <v>0.6893050670623779</v>
       </c>
       <c r="W2" t="n">
-        <v>0.885217010974884</v>
+        <v>0.7903205156326294</v>
       </c>
       <c r="X2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="AG2" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AH2" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AI2" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565883278846741</v>
+        <v>0.9563066959381104</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112817645072937</v>
+        <v>0.9114376902580261</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580537438392639</v>
+        <v>0.8578296899795532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622784733772278</v>
+        <v>0.6616203784942627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019806981086731</v>
+        <v>0.9018417000770569</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002016582438865534</v>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>23402514</v>
+        <v>4371144</v>
       </c>
       <c r="E3" t="n">
-        <v>1877181</v>
+        <v>666874</v>
       </c>
       <c r="F3" t="n">
-        <v>32045</v>
+        <v>11653</v>
       </c>
       <c r="G3" t="n">
-        <v>4111</v>
+        <v>1310</v>
       </c>
       <c r="H3" t="n">
-        <v>1874</v>
+        <v>854</v>
       </c>
       <c r="I3" t="n">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="J3" t="n">
-        <v>50347369</v>
+        <v>10069449</v>
       </c>
       <c r="K3" t="n">
-        <v>54680234</v>
+        <v>10598286</v>
       </c>
       <c r="L3" t="n">
-        <v>62962008</v>
+        <v>12161677</v>
       </c>
       <c r="M3" t="n">
-        <v>76488521</v>
+        <v>15165432</v>
       </c>
       <c r="N3" t="n">
-        <v>81484663</v>
+        <v>16267351</v>
       </c>
       <c r="O3" t="n">
-        <v>79104426</v>
+        <v>15751448</v>
       </c>
       <c r="P3" t="n">
-        <v>81005984</v>
+        <v>16186314</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.924344003200531</v>
+        <v>0.865250289440155</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8428260684013367</v>
+        <v>0.7137181162834167</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7631508708000183</v>
+        <v>0.5883642435073853</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4812933802604675</v>
+        <v>0.2650890648365021</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8280909061431885</v>
+        <v>0.6739963889122009</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8571599721908569</v>
+        <v>0.7073420286178589</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="Z3" t="n">
-        <v>995349</v>
+        <v>199108</v>
       </c>
       <c r="AA3" t="n">
-        <v>42884</v>
+        <v>8602</v>
       </c>
       <c r="AB3" t="n">
-        <v>34102</v>
+        <v>6851</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50348100</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>55661737</v>
+        <v>11143104</v>
       </c>
       <c r="AG3" t="n">
-        <v>64227600</v>
+        <v>12835014</v>
       </c>
       <c r="AH3" t="n">
-        <v>76746838</v>
+        <v>15348021</v>
       </c>
       <c r="AI3" t="n">
-        <v>81482703</v>
+        <v>16296339</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79283607</v>
+        <v>15856274</v>
       </c>
       <c r="AK3" t="n">
-        <v>81047145</v>
+        <v>16209353</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576305150985718</v>
+        <v>0.957513689994812</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099767208099365</v>
+        <v>0.9098963737487793</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575676679611206</v>
+        <v>0.8572810888290405</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618276834487915</v>
+        <v>0.6612800359725952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016205072402954</v>
+        <v>0.9016276001930237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03185715663591164</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>1969885</v>
+        <v>725543</v>
       </c>
       <c r="E4" t="n">
-        <v>13821964</v>
+        <v>2348204</v>
       </c>
       <c r="F4" t="n">
-        <v>549711</v>
+        <v>188936</v>
       </c>
       <c r="G4" t="n">
-        <v>18015</v>
+        <v>8478</v>
       </c>
       <c r="H4" t="n">
-        <v>37177</v>
+        <v>17539</v>
       </c>
       <c r="I4" t="n">
-        <v>2773</v>
+        <v>1388</v>
       </c>
       <c r="J4" t="n">
-        <v>731</v>
+        <v>171</v>
       </c>
       <c r="K4" t="n">
-        <v>2081796</v>
+        <v>765830</v>
       </c>
       <c r="L4" t="n">
-        <v>2718447</v>
+        <v>964223</v>
       </c>
       <c r="M4" t="n">
-        <v>920911</v>
+        <v>315450</v>
       </c>
       <c r="N4" t="n">
-        <v>148757</v>
+        <v>59230</v>
       </c>
       <c r="O4" t="n">
-        <v>428722</v>
+        <v>154846</v>
       </c>
       <c r="P4" t="n">
-        <v>107431</v>
+        <v>36293</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999884963035583</v>
+        <v>0.9999865293502808</v>
       </c>
       <c r="R4" t="n">
-        <v>0.921317458152771</v>
+        <v>0.8580242991447449</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8392217755317688</v>
+        <v>0.7113046050071716</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7785966396331787</v>
+        <v>0.6110648512840271</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5305273532867432</v>
+        <v>0.2750633955001831</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8295738101005554</v>
+        <v>0.6815647482872009</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8709626197814941</v>
+        <v>0.7465324997901917</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1027338</v>
+        <v>206350</v>
       </c>
       <c r="Z4" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AA4" t="n">
-        <v>415378</v>
+        <v>83345</v>
       </c>
       <c r="AB4" t="n">
-        <v>27557</v>
+        <v>5539</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1100293</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1452855</v>
+        <v>290886</v>
       </c>
       <c r="AH4" t="n">
-        <v>662594</v>
+        <v>132861</v>
       </c>
       <c r="AI4" t="n">
-        <v>150717</v>
+        <v>30242</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249541</v>
+        <v>50020</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571090936660767</v>
+        <v>0.9569098353385925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106287360191345</v>
+        <v>0.9106664061546326</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578105568885803</v>
+        <v>0.8575552701950073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620529890060425</v>
+        <v>0.661450207233429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018005132675171</v>
+        <v>0.9017346501350403</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>70456</v>
+        <v>26316</v>
       </c>
       <c r="E5" t="n">
-        <v>735621</v>
+        <v>254154</v>
       </c>
       <c r="F5" t="n">
-        <v>3564348</v>
+        <v>550190</v>
       </c>
       <c r="G5" t="n">
-        <v>61004</v>
+        <v>21483</v>
       </c>
       <c r="H5" t="n">
-        <v>224322</v>
+        <v>76171</v>
       </c>
       <c r="I5" t="n">
-        <v>14776</v>
+        <v>6788</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1915456</v>
+        <v>680740</v>
       </c>
       <c r="L5" t="n">
-        <v>2577581</v>
+        <v>941896</v>
       </c>
       <c r="M5" t="n">
-        <v>1106220</v>
+        <v>384928</v>
       </c>
       <c r="N5" t="n">
-        <v>231644</v>
+        <v>65715</v>
       </c>
       <c r="O5" t="n">
-        <v>437827</v>
+        <v>166166</v>
       </c>
       <c r="P5" t="n">
-        <v>138067</v>
+        <v>56598</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999911189079285</v>
+        <v>0.9999895691871643</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9513005614280701</v>
+        <v>0.9118804931640625</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9354772567749023</v>
+        <v>0.8838865160942078</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9753029942512512</v>
+        <v>0.9573356509208679</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9953655004501343</v>
+        <v>0.9923888444900513</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9894426465034485</v>
+        <v>0.9804451465606689</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9970090389251709</v>
+        <v>0.9943414330482483</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40265</v>
+        <v>8089</v>
       </c>
       <c r="Z5" t="n">
-        <v>426214</v>
+        <v>85507</v>
       </c>
       <c r="AA5" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AB5" t="n">
-        <v>49808</v>
+        <v>9991</v>
       </c>
       <c r="AC5" t="n">
-        <v>145788</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1072710</v>
+        <v>214636</v>
       </c>
       <c r="AG5" t="n">
-        <v>1476341</v>
+        <v>296450</v>
       </c>
       <c r="AH5" t="n">
-        <v>665240</v>
+        <v>133459</v>
       </c>
       <c r="AI5" t="n">
-        <v>151021</v>
+        <v>30288</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250558</v>
+        <v>50141</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735257625579834</v>
+        <v>0.9734619855880737</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643129110336304</v>
+        <v>0.964221715927124</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838227033615112</v>
+        <v>0.9837768077850342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963238835334778</v>
+        <v>0.9963127374649048</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939071536064148</v>
+        <v>0.9938985705375671</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383641242981</v>
+        <v>0.9983823895454407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
-        <v>41010</v>
+        <v>13649</v>
       </c>
       <c r="E6" t="n">
-        <v>61822</v>
+        <v>19449</v>
       </c>
       <c r="F6" t="n">
-        <v>83621</v>
+        <v>20669</v>
       </c>
       <c r="G6" t="n">
-        <v>214936</v>
+        <v>23704</v>
       </c>
       <c r="H6" t="n">
-        <v>41308</v>
+        <v>10760</v>
       </c>
       <c r="I6" t="n">
-        <v>3744</v>
+        <v>1139</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32411</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>26831</v>
+        <v>5380</v>
       </c>
       <c r="AA6" t="n">
-        <v>54451</v>
+        <v>10917</v>
       </c>
       <c r="AB6" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AC6" t="n">
-        <v>34923</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>368</v>
+        <v>299</v>
       </c>
       <c r="E7" t="n">
-        <v>41696</v>
+        <v>22597</v>
       </c>
       <c r="F7" t="n">
-        <v>247204</v>
+        <v>89905</v>
       </c>
       <c r="G7" t="n">
-        <v>62487</v>
+        <v>26386</v>
       </c>
       <c r="H7" t="n">
-        <v>2109025</v>
+        <v>343540</v>
       </c>
       <c r="I7" t="n">
-        <v>85930</v>
+        <v>26949</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4056</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148230</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37923</v>
+        <v>7595</v>
       </c>
       <c r="AC7" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>2127</v>
+        <v>1149</v>
       </c>
       <c r="F8" t="n">
-        <v>8330</v>
+        <v>4287</v>
       </c>
       <c r="G8" t="n">
-        <v>3140</v>
+        <v>1573</v>
       </c>
       <c r="H8" t="n">
-        <v>124041</v>
+        <v>49522</v>
       </c>
       <c r="I8" t="n">
-        <v>828518</v>
+        <v>136795</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
